--- a/LoanOfficer-A/2023/88 Rambhabati.xlsx
+++ b/LoanOfficer-A/2023/88 Rambhabati.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>319200</v>
+        <v>315600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -906,9 +906,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45650</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -932,9 +938,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45651</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -958,9 +970,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45652</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>

--- a/LoanOfficer-A/2023/88 Rambhabati.xlsx
+++ b/LoanOfficer-A/2023/88 Rambhabati.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>4800</v>
+        <v>16800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>315600</v>
+        <v>303600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1002,9 +1002,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45655</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1028,9 +1034,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45656</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1054,9 +1066,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45658</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1080,9 +1098,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45661</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1106,9 +1130,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45662</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1132,9 +1162,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45662</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1158,9 +1194,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45663</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1184,9 +1226,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45664</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1210,9 +1258,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45666</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1236,9 +1290,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45666</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>

--- a/LoanOfficer-A/2023/88 Rambhabati.xlsx
+++ b/LoanOfficer-A/2023/88 Rambhabati.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>16800</v>
+        <v>20400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>303600</v>
+        <v>300000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1322,9 +1322,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45669</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1348,9 +1354,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45672</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1374,9 +1386,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45674</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>

--- a/LoanOfficer-A/2023/88 Rambhabati.xlsx
+++ b/LoanOfficer-A/2023/88 Rambhabati.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>20400</v>
+        <v>44400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>300000</v>
+        <v>276000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45695</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -918,9 +924,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45695</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -950,9 +962,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45695</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -982,9 +1000,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45695</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1014,9 +1038,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45695</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1046,9 +1076,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45695</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1078,9 +1114,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45696</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1418,9 +1460,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45676</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1444,9 +1492,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45677</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1470,9 +1524,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45678</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1496,9 +1556,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45682</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1522,9 +1588,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45682</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1548,9 +1620,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45682</v>
+      </c>
+      <c r="C25" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1574,9 +1652,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45682</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1600,9 +1684,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45695</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1626,9 +1716,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45695</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1652,9 +1748,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45695</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1678,9 +1780,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45695</v>
+      </c>
+      <c r="C30" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1704,9 +1812,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45695</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1730,9 +1844,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45695</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/88 Rambhabati.xlsx
+++ b/LoanOfficer-A/2023/88 Rambhabati.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>44400</v>
+        <v>49200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>276000</v>
+        <v>271200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1152,9 +1152,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45699</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1184,9 +1190,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45699</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1216,9 +1228,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45700</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1248,9 +1266,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45702</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>

--- a/LoanOfficer-A/2023/88 Rambhabati.xlsx
+++ b/LoanOfficer-A/2023/88 Rambhabati.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>49200</v>
+        <v>50400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>271200</v>
+        <v>270000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1304,9 +1304,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45710</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>

--- a/LoanOfficer-A/2023/88 Rambhabati.xlsx
+++ b/LoanOfficer-A/2023/88 Rambhabati.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>50400</v>
+        <v>52800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>270000</v>
+        <v>267600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1342,9 +1342,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45730</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1374,9 +1380,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45730</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1200</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>

--- a/LoanOfficer-A/2023/88 Rambhabati.xlsx
+++ b/LoanOfficer-A/2023/88 Rambhabati.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD50000.15-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
